--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.34-privacy-and-pii/WKBK/90_workbooks/ISMS_A_5_34_4_TOMs_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.34-privacy-and-pii/WKBK/90_workbooks/ISMS_A_5_34_4_TOMs_Assessment_20260208.xlsx
@@ -14243,7 +14243,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Generated: 08.02.2026 11:49</t>
+          <t>Generated: 08.02.2026 12:25</t>
         </is>
       </c>
     </row>
